--- a/ksoft/docs/fields_details/jalmeida/CE0302(1).xlsx
+++ b/ksoft/docs/fields_details/jalmeida/CE0302(1).xlsx
@@ -7211,13 +7211,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79FDE671-F04A-4FB3-B00B-4FFFC0C252D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAFA8050-CBF3-4AC3-9DE5-BC206818EF42}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25679695-C41C-407C-B13A-710F1BAE146C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887892A6-F10F-42E6-AE74-8EB02FAA4BCE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1CCA1F0-CC4C-4552-8C37-305E842E445A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8961B1B5-7759-4DE9-882C-516E7A0BCBE2}"/>
 </file>
--- a/ksoft/docs/fields_details/jalmeida/CE0302(1).xlsx
+++ b/ksoft/docs/fields_details/jalmeida/CE0302(1).xlsx
@@ -7211,13 +7211,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAFA8050-CBF3-4AC3-9DE5-BC206818EF42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79FDE671-F04A-4FB3-B00B-4FFFC0C252D0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887892A6-F10F-42E6-AE74-8EB02FAA4BCE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25679695-C41C-407C-B13A-710F1BAE146C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8961B1B5-7759-4DE9-882C-516E7A0BCBE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1CCA1F0-CC4C-4552-8C37-305E842E445A}"/>
 </file>